--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -51,7 +51,7 @@
     <t>Заказчик</t>
   </si>
   <si>
-    <t xml:space="preserve">     {organization.organization}, {organization.address}
+    <t xml:space="preserve">     {organization.organization}, город {organization.city}, {organization.index}, район {organization.address}
          </t>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -127,10 +127,10 @@
     <t>{nights}</t>
   </si>
   <si>
-    <t>{organization.costPerDay}</t>
-  </si>
-  <si>
-    <t>{totalPrice}</t>
+    <t>{costPerDayFormatted}</t>
+  </si>
+  <si>
+    <t>{totalCost}</t>
   </si>
   <si>
     <t>Итого</t>
@@ -142,7 +142,7 @@
     <t xml:space="preserve">Сведения об использовании запасов, полученных от заказчика</t>
   </si>
   <si>
-    <t xml:space="preserve">{totalPriceWords} тенге 00 тиын</t>
+    <t xml:space="preserve">{totalCostRu} тенге 00 тиын</t>
   </si>
   <si>
     <t xml:space="preserve">наименование, количество, стоимость</t>

--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -51,11 +51,11 @@
     <t>Заказчик</t>
   </si>
   <si>
-    <t xml:space="preserve">     {organization.organization}, город {organization.city}, {organization.index}, район {organization.address}
+    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, район {customer.organization.address}
          </t>
   </si>
   <si>
-    <t>{organization.bin}</t>
+    <t>{customer.organization.bin}</t>
   </si>
   <si>
     <t>Исполнитель</t>

--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -51,7 +51,7 @@
     <t>Заказчик</t>
   </si>
   <si>
-    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index}, район {customer.organization.address}
+    <t xml:space="preserve">     {customer.organization.organization}, город {customer.organization.city}, {customer.organization.index} район {customer.organization.address}
          </t>
   </si>
   <si>

--- a/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
+++ b/apps/excel-service/templates/XANSHA/Completed Work Certificates.xlsx
@@ -142,7 +142,7 @@
     <t xml:space="preserve">Сведения об использовании запасов, полученных от заказчика</t>
   </si>
   <si>
-    <t xml:space="preserve">{totalCostRu} тенге 00 тиын</t>
+    <t xml:space="preserve">{totalCostRu} тенге{totalCostCentsRu} тиын</t>
   </si>
   <si>
     <t xml:space="preserve">наименование, количество, стоимость</t>
